--- a/duoki_editor/resources/data/blank/动物园-一般疑问句_否定答句跟读-1-blank.xlsx
+++ b/duoki_editor/resources/data/blank/动物园-一般疑问句_否定答句跟读-1-blank.xlsx
@@ -130,10 +130,10 @@
     <t>`我来帮你吧！[{word_en}]`</t>
   </si>
   <si>
-    <t>太棒了！{user_name}，动物朋友们的乐队表演真精彩呀！它们都是谁呢？它是一头猪吗？Is it a pig?</t>
-  </si>
-  <si>
-    <t>那这位动物朋友呢？它是一只狗吗？Is it a dog?</t>
+    <t>太棒了！{user_name}，动物朋友们的乐队表演真精彩呀！它们都是谁呢？它是一条狗吗？Is it a dog?</t>
+  </si>
+  <si>
+    <t>那这位动物朋友呢？它是一只猴子吗？Is it a monkey?</t>
   </si>
   <si>
     <t>这个呢？它是一只猫吗？Is it a cat?</t>
